--- a/product-definitions/spreadsheet/aerosol-optical-depth.xlsx
+++ b/product-definitions/spreadsheet/aerosol-optical-depth.xlsx
@@ -135,7 +135,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -161,14 +161,9 @@
     <font>
       <color theme="1"/>
       <name val="Arial"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <color theme="1"/>
       <name val="Arial"/>
     </font>
   </fonts>
@@ -186,7 +181,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -207,7 +202,6 @@
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="top"/>
     </xf>
@@ -223,13 +217,13 @@
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="0"/>
     </xf>
   </cellXfs>
@@ -1607,31 +1601,31 @@
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="8" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="8" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="9" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C6" s="7"/>
@@ -1640,7 +1634,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="7" t="s">
         <v>16</v>
       </c>
       <c r="C7" s="7" t="s">
@@ -1648,34 +1642,34 @@
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="11">
+      <c r="C8" s="10">
         <v>-1.0E20</v>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="C9" s="11" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="11" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C11" s="8" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1688,31 +1682,31 @@
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="C14" s="8" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="8" t="s">
+      <c r="B15" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="C15" s="8" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="8" t="s">
+      <c r="B16" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="C16" s="10">
+      <c r="C16" s="9">
         <v>1.0</v>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="8" t="s">
+      <c r="B17" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C17" s="7" t="s">
@@ -1721,7 +1715,7 @@
       <c r="D17" s="7"/>
     </row>
     <row r="18">
-      <c r="B18" s="8" t="s">
+      <c r="B18" s="7" t="s">
         <v>16</v>
       </c>
       <c r="C18" s="7" t="s">
@@ -1729,81 +1723,81 @@
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="8" t="s">
+      <c r="B19" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C19" s="11">
+      <c r="C19" s="10">
         <v>-1.0E20</v>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="8" t="s">
+      <c r="B20" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C20" s="12" t="s">
+      <c r="C20" s="11" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="21">
-      <c r="B21" s="8" t="s">
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="B21" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C21" s="12" t="s">
+      <c r="C21" s="11" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="22">
-      <c r="B22" s="13" t="s">
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="B22" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="C22" s="13"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14" t="s">
+      <c r="C22" s="12"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="13" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="23">
-      <c r="B23" s="8" t="s">
+    <row r="23" ht="15.75" customHeight="1">
+      <c r="B23" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="C23" s="9" t="s">
+      <c r="C23" s="8" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="24">
-      <c r="C24" s="9"/>
-    </row>
-    <row r="25">
+    <row r="24" ht="15.75" customHeight="1">
+      <c r="C24" s="8"/>
+    </row>
+    <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="7" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="26">
-      <c r="B26" s="8" t="s">
+    <row r="26" ht="15.75" customHeight="1">
+      <c r="B26" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C26" s="9" t="s">
+      <c r="C26" s="8" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="27">
-      <c r="B27" s="8" t="s">
+    <row r="27" ht="15.75" customHeight="1">
+      <c r="B27" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C27" s="9" t="s">
+      <c r="C27" s="8" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="28">
-      <c r="B28" s="8" t="s">
+    <row r="28" ht="15.75" customHeight="1">
+      <c r="B28" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="C28" s="9">
+      <c r="C28" s="8">
         <v>1.0</v>
       </c>
     </row>
-    <row r="29">
-      <c r="B29" s="8" t="s">
+    <row r="29" ht="15.75" customHeight="1">
+      <c r="B29" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C29" s="7" t="s">
@@ -1811,148 +1805,148 @@
       </c>
       <c r="D29" s="7"/>
     </row>
-    <row r="30">
-      <c r="B30" s="8" t="s">
+    <row r="30" ht="15.75" customHeight="1">
+      <c r="B30" s="7" t="s">
         <v>16</v>
       </c>
       <c r="C30" s="7" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="31">
-      <c r="B31" s="8" t="s">
+    <row r="31" ht="15.75" customHeight="1">
+      <c r="B31" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C31" s="11">
+      <c r="C31" s="10">
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="32">
-      <c r="B32" s="8" t="s">
+    <row r="32" ht="15.75" customHeight="1">
+      <c r="B32" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C32" s="12" t="s">
+      <c r="C32" s="11" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="33">
-      <c r="B33" s="8" t="s">
+    <row r="33" ht="15.75" customHeight="1">
+      <c r="B33" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C33" s="12" t="s">
+      <c r="C33" s="11" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="34">
-      <c r="B34" s="13" t="s">
+    <row r="34" ht="15.75" customHeight="1">
+      <c r="B34" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="C34" s="13"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14" t="s">
+      <c r="C34" s="12"/>
+      <c r="D34" s="13"/>
+      <c r="E34" s="13" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="35">
-      <c r="B35" s="8" t="s">
+    <row r="35" ht="15.75" customHeight="1">
+      <c r="B35" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="C35" s="9" t="s">
+      <c r="C35" s="8" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="36">
-      <c r="C36" s="9"/>
-    </row>
-    <row r="37">
+    <row r="36" ht="15.75" customHeight="1">
+      <c r="C36" s="8"/>
+    </row>
+    <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="C37" s="9"/>
-    </row>
-    <row r="38">
-      <c r="B38" s="8" t="s">
+      <c r="C37" s="8"/>
+    </row>
+    <row r="38" ht="15.75" customHeight="1">
+      <c r="B38" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C38" s="9" t="s">
+      <c r="C38" s="8" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="39">
-      <c r="B39" s="8" t="s">
+    <row r="39" ht="15.75" customHeight="1">
+      <c r="B39" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C39" s="9" t="s">
+      <c r="C39" s="8" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="40">
-      <c r="B40" s="8" t="s">
+    <row r="40" ht="15.75" customHeight="1">
+      <c r="B40" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="C40" s="10">
+      <c r="C40" s="9">
         <v>1.0</v>
       </c>
     </row>
-    <row r="41">
-      <c r="B41" s="8" t="s">
+    <row r="41" ht="15.75" customHeight="1">
+      <c r="B41" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C41" s="10"/>
-    </row>
-    <row r="42">
-      <c r="B42" s="8" t="s">
+      <c r="C41" s="9"/>
+    </row>
+    <row r="42" ht="15.75" customHeight="1">
+      <c r="B42" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C42" s="9" t="s">
+      <c r="C42" s="8" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="43">
-      <c r="B43" s="15" t="s">
+    <row r="43" ht="15.75" customHeight="1">
+      <c r="B43" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="C43" s="13" t="s">
+      <c r="C43" s="12" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="44">
-      <c r="B44" s="14" t="s">
+    <row r="44" ht="15.75" customHeight="1">
+      <c r="B44" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C44" s="16" t="s">
+      <c r="C44" s="15" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="45" ht="12.0" customHeight="1"/>
     <row r="46" ht="12.0" customHeight="1">
-      <c r="C46" s="9"/>
+      <c r="C46" s="8"/>
     </row>
     <row r="47" ht="12.0" customHeight="1">
-      <c r="C47" s="9"/>
+      <c r="C47" s="8"/>
     </row>
     <row r="48" ht="12.0" customHeight="1">
-      <c r="C48" s="9"/>
+      <c r="C48" s="8"/>
     </row>
     <row r="49" ht="12.0" customHeight="1">
-      <c r="C49" s="9"/>
+      <c r="C49" s="8"/>
     </row>
     <row r="50" ht="12.0" customHeight="1">
-      <c r="C50" s="10"/>
+      <c r="C50" s="9"/>
     </row>
     <row r="51" ht="12.0" customHeight="1">
-      <c r="C51" s="10"/>
+      <c r="C51" s="9"/>
     </row>
     <row r="52" ht="12.0" customHeight="1">
-      <c r="C52" s="9"/>
+      <c r="C52" s="8"/>
     </row>
     <row r="53" ht="12.0" customHeight="1">
-      <c r="B53" s="15"/>
-      <c r="C53" s="13"/>
+      <c r="B53" s="14"/>
+      <c r="C53" s="12"/>
     </row>
     <row r="54" ht="12.0" customHeight="1">
-      <c r="B54" s="14"/>
-      <c r="C54" s="16"/>
+      <c r="B54" s="13"/>
+      <c r="C54" s="15"/>
     </row>
     <row r="55" ht="12.0" customHeight="1"/>
     <row r="56" ht="12.0" customHeight="1"/>
